--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87382</v>
+        <v>87386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90885</v>
+        <v>90889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90885</v>
+        <v>90889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87501</v>
+        <v>87505</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87501</v>
+        <v>87505</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90889</v>
+        <v>90891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90889</v>
+        <v>90891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90891</v>
+        <v>90904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90891</v>
+        <v>90904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87586</v>
+        <v>87599</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87507</v>
+        <v>87520</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87507</v>
+        <v>87520</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90904</v>
+        <v>90906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90904</v>
+        <v>90906</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87520</v>
+        <v>87522</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87520</v>
+        <v>87522</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90906</v>
+        <v>90909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90906</v>
+        <v>90909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87522</v>
+        <v>87525</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87522</v>
+        <v>87525</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90909</v>
+        <v>90919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90909</v>
+        <v>90919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87525</v>
+        <v>87535</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87525</v>
+        <v>87535</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90919</v>
+        <v>90920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90919</v>
+        <v>90920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87535</v>
+        <v>87536</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87535</v>
+        <v>87536</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90920</v>
+        <v>90923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90920</v>
+        <v>90923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87536</v>
+        <v>87539</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87536</v>
+        <v>87539</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90923</v>
+        <v>90928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90923</v>
+        <v>90928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87539</v>
+        <v>87544</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87539</v>
+        <v>87544</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90928</v>
+        <v>90939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90928</v>
+        <v>90939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87544</v>
+        <v>87555</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87544</v>
+        <v>87555</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90939</v>
+        <v>90940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90939</v>
+        <v>90940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87555</v>
+        <v>87556</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87555</v>
+        <v>87556</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>90943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90940</v>
+        <v>90943</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140181</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140489</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137140492</v>
       </c>
       <c r="B4" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137140497</v>
       </c>
       <c r="B5" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137140512</v>
       </c>
       <c r="B6" t="n">
-        <v>90943</v>
+        <v>90947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137140515</v>
       </c>
       <c r="B7" t="n">
-        <v>90943</v>
+        <v>90947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>137140169</v>
       </c>
       <c r="B8" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137140148</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>137140151</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137140156</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137140159</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137140165</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137140168</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137140173</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137140178</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>137140182</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137140186</v>
       </c>
       <c r="B18" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137140187</v>
       </c>
       <c r="B19" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>137140192</v>
       </c>
       <c r="B20" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137140196</v>
       </c>
       <c r="B21" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>137140198</v>
       </c>
       <c r="B22" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>137140204</v>
       </c>
       <c r="B23" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>137140217</v>
       </c>
       <c r="B24" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>137140220</v>
       </c>
       <c r="B25" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137140222</v>
       </c>
       <c r="B26" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>137140485</v>
       </c>
       <c r="B27" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137140488</v>
       </c>
       <c r="B28" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>137140506</v>
       </c>
       <c r="B29" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>137140179</v>
       </c>
       <c r="B30" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>137140505</v>
       </c>
       <c r="B31" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>137140175</v>
       </c>
       <c r="B32" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>137140499</v>
       </c>
       <c r="B33" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137140160</v>
       </c>
       <c r="B34" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>137140166</v>
       </c>
       <c r="B35" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137140185</v>
       </c>
       <c r="B36" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137140210</v>
       </c>
       <c r="B37" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>137140214</v>
       </c>
       <c r="B38" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>137140490</v>
       </c>
       <c r="B39" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>137140493</v>
       </c>
       <c r="B40" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>137140498</v>
       </c>
       <c r="B41" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>137140504</v>
       </c>
       <c r="B42" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137140509</v>
       </c>
       <c r="B43" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>137140514</v>
       </c>
       <c r="B44" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>137140517</v>
       </c>
       <c r="B45" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>137140202</v>
       </c>
       <c r="B46" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>137140176</v>
       </c>
       <c r="B58" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>137140207</v>
       </c>
       <c r="B59" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>137140157</v>
       </c>
       <c r="B62" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>137140162</v>
       </c>
       <c r="B63" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>137140496</v>
       </c>
       <c r="B64" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>137140501</v>
       </c>
       <c r="B65" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>137140149</v>
       </c>
       <c r="B66" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137140152</v>
       </c>
       <c r="B67" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137140161</v>
       </c>
       <c r="B68" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137140163</v>
       </c>
       <c r="B69" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>137140174</v>
       </c>
       <c r="B70" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>137140184</v>
       </c>
       <c r="B71" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>137140201</v>
       </c>
       <c r="B72" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>137140211</v>
       </c>
       <c r="B73" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>137140215</v>
       </c>
       <c r="B74" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>137140224</v>
       </c>
       <c r="B75" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>137140486</v>
       </c>
       <c r="B76" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>137140502</v>
       </c>
       <c r="B77" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>137140507</v>
       </c>
       <c r="B78" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>137140508</v>
       </c>
       <c r="B79" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>137140513</v>
       </c>
       <c r="B80" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137140146</v>
       </c>
       <c r="B81" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>137140147</v>
       </c>
       <c r="B82" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>137140153</v>
       </c>
       <c r="B83" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>137140154</v>
       </c>
       <c r="B84" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>137140155</v>
       </c>
       <c r="B85" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>137140158</v>
       </c>
       <c r="B86" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>137140164</v>
       </c>
       <c r="B87" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>137140170</v>
       </c>
       <c r="B88" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>137140171</v>
       </c>
       <c r="B89" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>137140172</v>
       </c>
       <c r="B90" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>137140180</v>
       </c>
       <c r="B91" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>137140183</v>
       </c>
       <c r="B92" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>137140188</v>
       </c>
       <c r="B93" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>137140189</v>
       </c>
       <c r="B94" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>137140190</v>
       </c>
       <c r="B95" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>137140191</v>
       </c>
       <c r="B96" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>137140193</v>
       </c>
       <c r="B97" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>137140195</v>
       </c>
       <c r="B98" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>137140197</v>
       </c>
       <c r="B99" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>137140200</v>
       </c>
       <c r="B100" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>137140203</v>
       </c>
       <c r="B101" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137140205</v>
       </c>
       <c r="B102" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>137140206</v>
       </c>
       <c r="B103" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>137140212</v>
       </c>
       <c r="B104" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>137140213</v>
       </c>
       <c r="B105" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>137140218</v>
       </c>
       <c r="B106" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>137140487</v>
       </c>
       <c r="B107" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>137140491</v>
       </c>
       <c r="B108" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>137140494</v>
       </c>
       <c r="B109" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>137140495</v>
       </c>
       <c r="B110" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>137140500</v>
       </c>
       <c r="B111" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>137140503</v>
       </c>
       <c r="B112" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>137140510</v>
       </c>
       <c r="B113" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>137140516</v>
       </c>
       <c r="B114" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>137140219</v>
       </c>
       <c r="B115" t="n">
-        <v>87559</v>
+        <v>87563</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>137140223</v>
       </c>
       <c r="B116" t="n">
-        <v>87559</v>
+        <v>87563</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
